--- a/GearSage-client/pkgGear/data_raw/owner_hook_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/owner_hook_import.xlsx
@@ -9800,7 +9800,7 @@
         <v>Owner</v>
       </c>
       <c r="D170" t="str">
-        <v/>
+        <v>OHK1028-S3-0-Q5-N1</v>
       </c>
       <c r="E170" t="str">
         <v>特种钩</v>
@@ -9847,7 +9847,7 @@
         <v>Owner</v>
       </c>
       <c r="D171" t="str">
-        <v/>
+        <v>OHK1028-S4-0-Q4-N2</v>
       </c>
       <c r="E171" t="str">
         <v>特种钩</v>
@@ -9894,7 +9894,7 @@
         <v>Owner</v>
       </c>
       <c r="D172" t="str">
-        <v/>
+        <v>OHK1028-S5-0-Q4-N3</v>
       </c>
       <c r="E172" t="str">
         <v>特种钩</v>

--- a/GearSage-client/pkgGear/data_raw/owner_hook_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/owner_hook_import.xlsx
@@ -458,7 +458,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H2" t="str">
-        <v>pkgGear/images/hook/OWNER/jungle_drop_shot.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_drop_shot.gif</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -493,7 +493,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H3" t="str">
-        <v>pkgGear/images/hook/OWNER/multi_offset.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/multi_offset.gif</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -528,7 +528,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H4" t="str">
-        <v>pkgGear/images/hook/OWNER/ringed_all_purpose_softbait_hook.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/ringed_all_purpose_softbait_hook.gif</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -563,7 +563,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H5" t="str">
-        <v>pkgGear/images/hook/OWNER/haymaker.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/haymaker.gif</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -598,7 +598,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H6" t="str">
-        <v>pkgGear/images/hook/OWNER/offset_shank_wide_gap_red.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank_wide_gap_red.jpg</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -633,7 +633,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H7" t="str">
-        <v>pkgGear/images/hook/OWNER/flashy_swimmer_silver_colorado.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_silver_colorado.jpg</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -668,7 +668,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H8" t="str">
-        <v>pkgGear/images/hook/OWNER/flashy_swimmer_gold_willowleaf.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_gold_willowleaf.jpg</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -703,7 +703,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H9" t="str">
-        <v>pkgGear/images/hook/OWNER/jungle_flipping_hd.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_flipping_hd.gif</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -738,7 +738,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H10" t="str">
-        <v>pkgGear/images/hook/OWNER/cover_shot_hd.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/cover_shot_hd.gif</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -773,7 +773,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H11" t="str">
-        <v>pkgGear/images/hook/OWNER/sniper_finesse.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/sniper_finesse.gif</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -808,7 +808,7 @@
         <v>倒钓钩 / Wacky</v>
       </c>
       <c r="H12" t="str">
-        <v>pkgGear/images/hook/OWNER/jungle_wacky.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_wacky.gif</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -843,7 +843,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H13" t="str">
-        <v>pkgGear/images/hook/OWNER/flashy_swimmer_gold_colorado.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_gold_colorado.gif</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -878,7 +878,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H14" t="str">
-        <v>pkgGear/images/hook/OWNER/jungle_wide_gap.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_wide_gap.gif</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -913,7 +913,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H15" t="str">
-        <v>pkgGear/images/hook/OWNER/cover_shot.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/cover_shot.gif</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -948,7 +948,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H16" t="str">
-        <v>pkgGear/images/hook/OWNER/offset_shank_wide_gap.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank_wide_gap.jpg</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -983,7 +983,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H17" t="str">
-        <v>pkgGear/images/hook/OWNER/toad_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/toad_hook.jpg</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1018,7 +1018,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H18" t="str">
-        <v>pkgGear/images/hook/OWNER/wide_gap_plus.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/wide_gap_plus.jpg</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H19" t="str">
-        <v>pkgGear/images/hook/OWNER/stinger_harness_rig.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/stinger_harness_rig.gif</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1088,7 +1088,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H20" t="str">
-        <v>pkgGear/images/hook/OWNER/twistlock_light_weighted.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_light_weighted.jpg</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H21" t="str">
-        <v>pkgGear/images/hook/OWNER/j_light.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/j_light.gif</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1158,7 +1158,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H22" t="str">
-        <v>pkgGear/images/hook/OWNER/rig_n_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/rig_n_hook.jpg</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1193,7 +1193,7 @@
         <v>倒钓钩 / Wacky</v>
       </c>
       <c r="H23" t="str">
-        <v>pkgGear/images/hook/OWNER/wacky_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/wacky_hook.jpg</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1228,7 +1228,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H24" t="str">
-        <v>pkgGear/images/hook/OWNER/twistlock_3x_weighted.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_3x_weighted.jpg</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1263,7 +1263,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H25" t="str">
-        <v>pkgGear/images/hook/OWNER/twistlock_3x.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_3x.jpg</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1298,7 +1298,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H26" t="str">
-        <v>pkgGear/images/hook/OWNER/beast_weighted.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/beast_weighted.jpg</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1333,7 +1333,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H27" t="str">
-        <v>pkgGear/images/hook/OWNER/beast_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/beast_hook.jpg</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1368,7 +1368,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H28" t="str">
-        <v>pkgGear/images/hook/OWNER/flashy_swimmer_beast_version.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_beast_version.gif</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1403,7 +1403,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H29" t="str">
-        <v>pkgGear/images/hook/OWNER/twistlock_light.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_light.jpg</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1438,7 +1438,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H30" t="str">
-        <v>pkgGear/images/hook/OWNER/twistlock_flipping_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_flipping_hook.jpg</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1473,7 +1473,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H31" t="str">
-        <v>pkgGear/images/hook/OWNER/all_purpose_softbait_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/all_purpose_softbait_hook.jpg</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1508,7 +1508,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H32" t="str">
-        <v>pkgGear/images/hook/OWNER/all_purpose_worm_hook.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/all_purpose_worm_hook.gif</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1543,7 +1543,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H33" t="str">
-        <v>pkgGear/images/hook/OWNER/jungle_flipping_hook.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_flipping_hook.gif</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1578,7 +1578,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H34" t="str">
-        <v>pkgGear/images/hook/OWNER/oversize_worm_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/oversize_worm_hook.jpg</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1613,7 +1613,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H35" t="str">
-        <v>pkgGear/images/hook/OWNER/j_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/j_hook.jpg</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1648,7 +1648,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H36" t="str">
-        <v>pkgGear/images/hook/OWNER/straight_shank_wide_gap.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/straight_shank_wide_gap.jpg</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1683,7 +1683,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H37" t="str">
-        <v>pkgGear/images/hook/OWNER/straight_shank.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/straight_shank.jpg</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1718,7 +1718,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H38" t="str">
-        <v>pkgGear/images/hook/OWNER/phantom_tube_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/phantom_tube_hook.jpg</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1753,7 +1753,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H39" t="str">
-        <v>pkgGear/images/hook/OWNER/mosquito_hook.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/mosquito_hook.gif</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1788,7 +1788,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H40" t="str">
-        <v>pkgGear/images/hook/OWNER/offset_shank.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank.jpg</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1823,7 +1823,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H41" t="str">
-        <v>pkgGear/images/hook/OWNER/flashy_swimmer_silver_willowleaf.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_silver_willowleaf.jpg</v>
       </c>
       <c r="I41" t="str">
         <v/>

--- a/GearSage-client/pkgGear/data_raw/owner_hook_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/owner_hook_import.xlsx
@@ -455,7 +455,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H2" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_drop_shot.gif</v>
@@ -490,7 +490,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H3" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/multi_offset.gif</v>
@@ -525,7 +525,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H4" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/ringed_all_purpose_softbait_hook.gif</v>
@@ -560,7 +560,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H5" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/haymaker.gif</v>
@@ -595,7 +595,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H6" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank_wide_gap_red.jpg</v>
@@ -630,7 +630,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H7" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_silver_colorado.jpg</v>
@@ -665,7 +665,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H8" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_gold_willowleaf.jpg</v>
@@ -700,7 +700,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>直柄钩</v>
       </c>
       <c r="H9" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_flipping_hd.gif</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H10" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/cover_shot_hd.gif</v>
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H11" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/sniper_finesse.gif</v>
@@ -805,7 +805,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>倒钓钩 / Wacky</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H12" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_wacky.gif</v>
@@ -840,7 +840,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H13" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_gold_colorado.gif</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H14" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_wide_gap.gif</v>
@@ -910,7 +910,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H15" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/cover_shot.gif</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H16" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank_wide_gap.jpg</v>
@@ -980,7 +980,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H17" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/toad_hook.jpg</v>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H18" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/wide_gap_plus.jpg</v>
@@ -1050,7 +1050,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>辅助挂钩</v>
       </c>
       <c r="H19" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/stinger_harness_rig.gif</v>
@@ -1085,7 +1085,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H20" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_light_weighted.jpg</v>
@@ -1120,7 +1120,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H21" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/j_light.gif</v>
@@ -1155,7 +1155,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H22" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/rig_n_hook.jpg</v>
@@ -1190,7 +1190,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>倒钓钩 / Wacky</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H23" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/wacky_hook.jpg</v>
@@ -1225,7 +1225,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H24" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_3x_weighted.jpg</v>
@@ -1260,7 +1260,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H25" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_3x.jpg</v>
@@ -1295,7 +1295,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H26" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/beast_weighted.jpg</v>
@@ -1330,7 +1330,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H27" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/beast_hook.jpg</v>
@@ -1365,7 +1365,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H28" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_beast_version.gif</v>
@@ -1400,7 +1400,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H29" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_light.jpg</v>
@@ -1435,7 +1435,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>直柄钩</v>
       </c>
       <c r="H30" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_flipping_hook.jpg</v>
@@ -1470,7 +1470,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H31" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/all_purpose_softbait_hook.jpg</v>
@@ -1505,7 +1505,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H32" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/all_purpose_worm_hook.gif</v>
@@ -1540,7 +1540,7 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>直柄钩</v>
       </c>
       <c r="H33" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_flipping_hook.gif</v>
@@ -1575,7 +1575,7 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H34" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/oversize_worm_hook.jpg</v>
@@ -1610,7 +1610,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H35" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/j_hook.jpg</v>
@@ -1645,7 +1645,7 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>直柄钩</v>
       </c>
       <c r="H36" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/straight_shank_wide_gap.jpg</v>
@@ -1680,7 +1680,7 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>直柄钩</v>
       </c>
       <c r="H37" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/straight_shank.jpg</v>
@@ -1715,7 +1715,7 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H38" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/phantom_tube_hook.jpg</v>
@@ -1750,7 +1750,7 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H39" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/mosquito_hook.gif</v>
@@ -1785,7 +1785,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H40" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank.jpg</v>
@@ -1820,7 +1820,7 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H41" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_silver_willowleaf.jpg</v>
